--- a/public/report_templates/caja/reportes/vchEnvio.xlsx
+++ b/public/report_templates/caja/reportes/vchEnvio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredipymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5BBCE5-AFF3-4F6A-B656-5F33556A1866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07789F7-D501-42E2-AABC-3BB62F584D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
   <sheets>
     <sheet name="vchEnvio" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>CONCEPTO</t>
   </si>
@@ -72,10 +72,7 @@
     <t>A USUARIO:</t>
   </si>
   <si>
-    <t>GRUPO CREDIPYME</t>
-  </si>
-  <si>
-    <t>RUC: 20611432616</t>
+    <t>CREDIPYME HUANCA SAC</t>
   </si>
 </sst>
 </file>
@@ -199,6 +196,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -207,21 +219,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -547,18 +544,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
     </row>
     <row r="3" spans="1:3" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -569,51 +564,51 @@
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="9"/>
+      <c r="C4" s="14"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="9"/>
+      <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
     </row>
     <row r="10" spans="1:3" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -624,8 +619,8 @@
       <c r="A11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:3" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
@@ -636,33 +631,33 @@
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="12"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="13"/>
+      <c r="C14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.27559055118110237" right="0" top="3.937007874015748E-2" bottom="0" header="0" footer="0"/>

--- a/public/report_templates/caja/reportes/vchEnvio.xlsx
+++ b/public/report_templates/caja/reportes/vchEnvio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07789F7-D501-42E2-AABC-3BB62F584D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E19171-59BE-49C4-8C52-2EE2916BF6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
   <sheets>
     <sheet name="vchEnvio" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
     <t>A USUARIO:</t>
   </si>
   <si>
-    <t>CREDIPYME HUANCA SAC</t>
+    <t>CREDIPYME HUANCA S.A.C</t>
   </si>
 </sst>
 </file>
@@ -196,6 +196,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -210,15 +219,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -544,16 +544,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -564,51 +564,51 @@
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="12"/>
+      <c r="C5" s="7"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="7"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:3" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -619,8 +619,8 @@
       <c r="A11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:3" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
@@ -631,33 +631,33 @@
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="12"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.27559055118110237" right="0" top="3.937007874015748E-2" bottom="0" header="0" footer="0"/>
